--- a/data/city_tax_settlement_status_r2/0097.xlsx
+++ b/data/city_tax_settlement_status_r2/0097.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\File01\納税課\03 税制係\（整理中）参考保存 ※現在は使用していないもの\オープンデータ\R6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ivpf201v.takamatsu.local\Profile\t10202\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E832D7F9-3DC1-41EF-A6CC-F4B7EADD1C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88CF8FD0-5263-4673-BB74-4C2E8C42CC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$B$1:$K$22</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="52">
   <si>
     <t>#property</t>
   </si>
@@ -31,154 +34,152 @@
     <t>taxItem</t>
   </si>
   <si>
+    <t>carryoverClassification</t>
+  </si>
+  <si>
+    <t>adjustedAmount</t>
+  </si>
+  <si>
+    <t>incomeAmount</t>
+  </si>
+  <si>
+    <t>nonPaymentDeficit</t>
+  </si>
+  <si>
+    <t>unpaidIncome</t>
+  </si>
+  <si>
+    <t>incomeRate</t>
+  </si>
+  <si>
+    <t>comparedToThePreviousYear</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>市民税</t>
+  </si>
+  <si>
+    <t>個人</t>
+  </si>
+  <si>
+    <t>現年課税分</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>滞納繰越分</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>法人</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>固定資産税</t>
+  </si>
+  <si>
+    <t>土地・家屋</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>償却資産</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>交付金</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>軽自動車税</t>
+  </si>
+  <si>
+    <t>種別割</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>環境性能割</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>－</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>市たばこ税</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>入湯税</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>事業所税</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>全税目</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>現年課税分滞納繰越分</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>令和6年度</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>taxItemContents</t>
-  </si>
-  <si>
-    <t>carryoverClassification</t>
-  </si>
-  <si>
-    <t>adjustedAmount</t>
-  </si>
-  <si>
-    <t>incomeAmount</t>
-  </si>
-  <si>
-    <t>nonPaymentDeficit</t>
-  </si>
-  <si>
-    <t>unpaidIncome</t>
-  </si>
-  <si>
-    <t>incomeRate</t>
-  </si>
-  <si>
-    <t>comparedToThePreviousYear</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>市民税</t>
-  </si>
-  <si>
-    <t>個人</t>
-  </si>
-  <si>
-    <t>現年課税分</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>滞納繰越分</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>法人</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>固定資産税</t>
-  </si>
-  <si>
-    <t>土地・家屋</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>償却資産</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>交付金</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>軽自動車税</t>
-  </si>
-  <si>
-    <t>種別割</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>環境性能割</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>－</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>市たばこ税</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>入湯税</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>事業所税</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>全税目</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>現年課税分滞納繰越分</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>令和5年度</t>
-  </si>
-  <si>
-    <t>令和5年度</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -586,20 +587,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.09765625" customWidth="1"/>
-    <col min="3" max="3" width="15.09765625" customWidth="1"/>
+    <col min="2" max="2" width="11.08203125" customWidth="1"/>
+    <col min="3" max="3" width="15.08203125" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="5" width="21.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.19921875" customWidth="1"/>
-    <col min="7" max="7" width="16.8984375" customWidth="1"/>
-    <col min="8" max="8" width="19.3984375" customWidth="1"/>
-    <col min="9" max="9" width="15.69921875" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" customWidth="1"/>
+    <col min="7" max="7" width="16.9140625" customWidth="1"/>
+    <col min="8" max="8" width="19.4140625" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -610,331 +611,332 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="1">
+        <v>23279743112</v>
+      </c>
+      <c r="G2" s="1">
+        <v>23100243740</v>
+      </c>
+      <c r="H2" s="1">
+        <v>96291</v>
+      </c>
+      <c r="I2" s="1">
+        <v>201236816</v>
+      </c>
+      <c r="J2" s="2">
+        <v>99.2</v>
+      </c>
+      <c r="K2" s="2">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1">
-        <v>24699660604</v>
-      </c>
-      <c r="G2" s="1">
-        <v>24502700421</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1917876</v>
-      </c>
-      <c r="I2" s="1">
-        <v>202470148</v>
-      </c>
-      <c r="J2" s="2">
-        <v>99.181089969930483</v>
-      </c>
-      <c r="K2" s="2">
-        <v>101.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F3" s="1">
+        <v>532403372</v>
+      </c>
+      <c r="G3" s="1">
+        <v>155810010</v>
+      </c>
+      <c r="H3" s="1">
+        <v>24587005</v>
+      </c>
+      <c r="I3" s="1">
+        <v>352193406</v>
+      </c>
+      <c r="J3" s="2">
+        <v>29.3</v>
+      </c>
+      <c r="K3" s="2">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1">
-        <v>549194597</v>
-      </c>
-      <c r="G3" s="1">
-        <v>186574140</v>
-      </c>
-      <c r="H3" s="1">
-        <v>28903205</v>
-      </c>
-      <c r="I3" s="1">
-        <v>333945870</v>
-      </c>
-      <c r="J3" s="2">
-        <v>34</v>
-      </c>
-      <c r="K3" s="2">
-        <v>99.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="F4" s="1">
+        <v>7533029300</v>
+      </c>
+      <c r="G4" s="1">
+        <v>7519597409</v>
+      </c>
+      <c r="H4" s="1">
+        <v>60000</v>
+      </c>
+      <c r="I4" s="1">
+        <v>21503691</v>
+      </c>
+      <c r="J4" s="2">
+        <v>99.8</v>
+      </c>
+      <c r="K4" s="2">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1">
-        <v>6572491300</v>
-      </c>
-      <c r="G4" s="1">
-        <v>6545925632</v>
-      </c>
-      <c r="H4" s="1">
-        <v>160000</v>
-      </c>
-      <c r="I4" s="1">
-        <v>26405668</v>
-      </c>
-      <c r="J4" s="2">
-        <v>99.6</v>
-      </c>
-      <c r="K4" s="2">
-        <v>94.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
+        <v>69909721</v>
+      </c>
+      <c r="G5" s="1">
+        <v>8210771</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3344147</v>
+      </c>
+      <c r="I5" s="1">
+        <v>58492803</v>
+      </c>
+      <c r="J5" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="K5" s="2">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1">
-        <v>58868576</v>
-      </c>
-      <c r="G5" s="1">
-        <v>10738014</v>
-      </c>
-      <c r="H5" s="1">
-        <v>4729309</v>
-      </c>
-      <c r="I5" s="1">
-        <v>43551553</v>
-      </c>
-      <c r="J5" s="2">
-        <v>18.2</v>
-      </c>
-      <c r="K5" s="2">
-        <v>76.099999999999994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1">
-        <v>23799769900</v>
+        <v>23845506200</v>
       </c>
       <c r="G6" s="1">
-        <v>23601407402</v>
+        <v>23645252894</v>
       </c>
       <c r="H6" s="1">
-        <v>5598500</v>
+        <v>8246271</v>
       </c>
       <c r="I6" s="1">
-        <v>193988898</v>
+        <v>193552735</v>
       </c>
       <c r="J6" s="2">
         <v>99.2</v>
       </c>
       <c r="K6" s="2">
+        <v>100.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1">
+        <v>644584316</v>
+      </c>
+      <c r="G7" s="1">
+        <v>155031633</v>
+      </c>
+      <c r="H7" s="1">
+        <v>47464807</v>
+      </c>
+      <c r="I7" s="1">
+        <v>442236278</v>
+      </c>
+      <c r="J7" s="2">
+        <v>24.1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>82.6</v>
+      </c>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3499590000</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3498011800</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1822000</v>
+      </c>
+      <c r="J8" s="2">
+        <v>100</v>
+      </c>
+      <c r="K8" s="2">
         <v>101.9</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="1">
-        <v>729318186</v>
-      </c>
-      <c r="G7" s="1">
-        <v>187750389</v>
-      </c>
-      <c r="H7" s="1">
-        <v>78750568</v>
-      </c>
-      <c r="I7" s="1">
-        <v>462911218</v>
-      </c>
-      <c r="J7" s="2">
-        <v>25.7</v>
-      </c>
-      <c r="K7" s="2">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3435696600</v>
-      </c>
-      <c r="G8" s="1">
-        <v>3433850000</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>2200100</v>
-      </c>
-      <c r="J8" s="2">
-        <v>99.939605996079123</v>
-      </c>
-      <c r="K8" s="2">
-        <v>98.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1">
+        <v>7103958</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2883427</v>
+      </c>
+      <c r="H9" s="1">
+        <v>851258</v>
+      </c>
+      <c r="I9" s="1">
+        <v>3369273</v>
+      </c>
+      <c r="J9" s="2">
+        <v>40.6</v>
+      </c>
+      <c r="K9" s="2">
+        <v>105.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1">
-        <v>8349000</v>
-      </c>
-      <c r="G9" s="1">
-        <v>2723742</v>
-      </c>
-      <c r="H9" s="1">
-        <v>721400</v>
-      </c>
-      <c r="I9" s="1">
-        <v>4903858</v>
-      </c>
-      <c r="J9" s="2">
-        <v>32.6</v>
-      </c>
-      <c r="K9" s="2">
-        <v>63.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1">
-        <v>258988200</v>
+        <v>254465700</v>
       </c>
       <c r="G10" s="1">
-        <v>258988200</v>
+        <v>254465700</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -946,65 +948,65 @@
         <v>100</v>
       </c>
       <c r="K10" s="2">
-        <v>100.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>98.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1361014200</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1342703787</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I11" s="1">
+        <v>18490204</v>
+      </c>
+      <c r="J11" s="2">
+        <v>98.7</v>
+      </c>
+      <c r="K11" s="2">
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1328767100</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1310135633</v>
-      </c>
-      <c r="H11" s="1">
-        <v>70800</v>
-      </c>
-      <c r="I11" s="1">
-        <v>18664639</v>
-      </c>
-      <c r="J11" s="2">
-        <v>98.6</v>
-      </c>
-      <c r="K11" s="2">
-        <v>103.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" s="1">
-        <v>57935400</v>
+        <v>83707100</v>
       </c>
       <c r="G12" s="1">
-        <v>57935400</v>
+        <v>83707100</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -1016,65 +1018,65 @@
         <v>100</v>
       </c>
       <c r="K12" s="2">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>144.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="1">
+        <v>56693044</v>
+      </c>
+      <c r="G13" s="1">
+        <v>13577609</v>
+      </c>
+      <c r="H13" s="1">
+        <v>5209888</v>
+      </c>
+      <c r="I13" s="1">
+        <v>37931447</v>
+      </c>
+      <c r="J13" s="2">
+        <v>23.9</v>
+      </c>
+      <c r="K13" s="2">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>35</v>
       </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="1">
-        <v>59000321</v>
-      </c>
-      <c r="G13" s="1">
-        <v>14527831</v>
-      </c>
-      <c r="H13" s="1">
-        <v>5851257</v>
-      </c>
-      <c r="I13" s="1">
-        <v>38628105</v>
-      </c>
-      <c r="J13" s="2">
-        <v>24.6</v>
-      </c>
-      <c r="K13" s="2">
-        <v>90.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="1">
-        <v>2997969112</v>
+        <v>2956407248</v>
       </c>
       <c r="G14" s="1">
-        <v>2997969112</v>
+        <v>2956407248</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -1086,295 +1088,295 @@
         <v>100</v>
       </c>
       <c r="K14" s="2">
-        <v>100.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>98.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
         <v>39</v>
       </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>40</v>
-      </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16" s="1">
-        <v>30957300</v>
+        <v>33259050</v>
       </c>
       <c r="G16" s="1">
-        <v>30957300</v>
+        <v>33256950</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J16" s="2">
         <v>100</v>
       </c>
       <c r="K16" s="2">
-        <v>116.5</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1">
-        <v>7650</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>7650</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
-      <c r="J17" s="2">
-        <v>0</v>
+      <c r="J17" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
         <v>42</v>
       </c>
-      <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" s="1">
-        <v>2346296600</v>
+        <v>2369353100</v>
       </c>
       <c r="G18" s="1">
-        <v>2343742400</v>
+        <v>2364997900</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>3075100</v>
       </c>
       <c r="I18" s="1">
-        <v>2554200</v>
+        <v>1923900</v>
       </c>
       <c r="J18" s="2">
-        <v>99.9</v>
+        <v>99.8</v>
       </c>
       <c r="K18" s="2">
-        <v>98.5</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1">
-        <v>33460900</v>
+        <v>21356800</v>
       </c>
       <c r="G19" s="1">
-        <v>5254100</v>
+        <v>7975969</v>
       </c>
       <c r="H19" s="1">
-        <v>9404200</v>
+        <v>12154831</v>
       </c>
       <c r="I19" s="1">
-        <v>18802600</v>
+        <v>1226000</v>
       </c>
       <c r="J19" s="2">
-        <v>15.7</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="K19" s="2">
-        <v>33.6</v>
+        <v>151.80000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
         <v>45</v>
       </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" t="s">
-        <v>46</v>
-      </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" s="1">
-        <v>65528532116</v>
+        <v>65216075010</v>
       </c>
       <c r="G20" s="1">
-        <v>65083611500</v>
+        <v>64798644528</v>
       </c>
       <c r="H20" s="1">
-        <v>7747176</v>
+        <v>11483662</v>
       </c>
       <c r="I20" s="1">
-        <v>446283653</v>
+        <v>438531446</v>
       </c>
       <c r="J20" s="2">
-        <v>99.275801897828273</v>
+        <v>99.4</v>
       </c>
       <c r="K20" s="2">
-        <v>100.6</v>
+        <v>99.6</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1">
-        <v>1438199230</v>
+        <v>1332051211</v>
       </c>
       <c r="G21" s="1">
-        <v>407568216</v>
+        <v>343489419</v>
       </c>
       <c r="H21" s="1">
-        <v>128367589</v>
+        <v>93611936</v>
       </c>
       <c r="I21" s="1">
-        <v>902743204</v>
+        <v>895449207</v>
       </c>
       <c r="J21" s="2">
-        <v>28.3</v>
+        <v>25.8</v>
       </c>
       <c r="K21" s="2">
-        <v>94.3</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" t="s">
-        <v>49</v>
-      </c>
       <c r="F22" s="1">
-        <v>66966731346</v>
+        <v>66548126221</v>
       </c>
       <c r="G22" s="1">
-        <v>65491179716</v>
+        <v>65142133947</v>
       </c>
       <c r="H22" s="1">
-        <v>136114765</v>
+        <v>105095598</v>
       </c>
       <c r="I22" s="1">
-        <v>1349026857</v>
+        <v>1333980653</v>
       </c>
       <c r="J22" s="2">
-        <v>97.8</v>
+        <v>97.9</v>
       </c>
       <c r="K22" s="2">
-        <v>100.5</v>
+        <v>99.5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="68" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A3:A22 A2 C2:E2 C20:E22 C3:E3 C4:E5 C6:E7 C8:E9 C10:E10 C11:E13 C14:E15 C16:E17 C18:E19" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A3:A22 A2 C2:E2 C20:E22 C3:E3 C4:E5 C6:E7 C8:E9 C10:E10 C11:E13 C14:E15 C16:E17 C18:E19 E1:K1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>